--- a/product-docs/.gitbook/assets/sample_folders.xlsx
+++ b/product-docs/.gitbook/assets/sample_folders.xlsx
@@ -1,127 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Folder" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Folder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACME Corp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root domain for ACME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All IT assets and</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Department</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human Resources scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial systems and data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free-text description of the folder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -146,14 +77,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -169,60 +100,56 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -463,146 +390,219 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col width="30" customWidth="1" style="5" min="1" max="1"/>
+    <col width="50" customWidth="1" style="5" min="2" max="2"/>
+    <col width="30" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+    <row r="1" ht="21.75" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>iam_group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="6">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Root domain for ACME</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="6">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>All IT assets and</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="6">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>HR Department</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Human Resources scope</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="6">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Financial systems and data</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>ACME Corp</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col width="20" customWidth="1" style="5" min="1" max="1"/>
+    <col width="12" customWidth="1" style="5" min="2" max="2"/>
+    <col width="90" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
+    <row r="1" ht="15" customHeight="1" s="6">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="6">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Unique name for the folder/domain. Used for conflict detection together with 'domain'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1" s="6">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Free-text description of the folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1" s="6">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Name of the parent folder. Leave blank to place the folder at root level. Must match exactly one existing folder name (case-insensitive). An error is returned when the name is ambiguous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>iam_group</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>When non-empty (e.g. 'x'), enables IAM group creation for the folder (create_iam_groups).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/product-docs/.gitbook/assets/sample_folders.xlsx
+++ b/product-docs/.gitbook/assets/sample_folders.xlsx
@@ -419,7 +419,7 @@
           <t>domain</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>iam_group</t>
         </is>
@@ -437,9 +437,9 @@
         </is>
       </c>
       <c r="C2" s="9" t="n"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>x</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>iam_group</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>When non-empty (e.g. 'x'), enables IAM group creation for the folder (create_iam_groups).</t>
         </is>
